--- a/data/경혈명_비교_정리_KJH.xlsx
+++ b/data/경혈명_비교_정리_KJH.xlsx
@@ -11519,7 +11519,7 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>김문</t>
+          <t>금문</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
